--- a/2025/salida_comparativo_p11/P11_2025_informe_alertas_mes06_vs_mes12.xlsx
+++ b/2025/salida_comparativo_p11/P11_2025_informe_alertas_mes06_vs_mes12.xlsx
@@ -23,16 +23,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -51,21 +48,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -441,22 +429,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seccion</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Total alertas</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Pasa a 0 en mes 12</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Baja de mes 6 a mes 12</t>
         </is>
@@ -668,782 +656,782 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Servicio de Salud</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Comuna</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Establecimiento</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo DEIS</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Prestacion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Detalle de prestacion</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Ano</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Codigo Servicio REM</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Codigo Comuna REM</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Total mes 6</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Total mes 12</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Diferencia</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Alerta</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>COL01 - TOTAL - Ambos sexos | Mes 6</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>COL01 - TOTAL - Ambos sexos | Mes 12</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>COL01 - TOTAL - Ambos sexos | Diferencia</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>COL02 - TOTAL - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>COL02 - TOTAL - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>COL02 - TOTAL - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>COL03 - TOTAL - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>COL03 - TOTAL - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>COL03 - TOTAL - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>COL04 - RANGO ETARIO Y SEXO - Menor 1 Año - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>COL04 - RANGO ETARIO Y SEXO - Menor 1 Año - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>COL04 - RANGO ETARIO Y SEXO - Menor 1 Año - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>COL05 - RANGO ETARIO Y SEXO - Menor 1 Año - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>COL05 - RANGO ETARIO Y SEXO - Menor 1 Año - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>COL05 - RANGO ETARIO Y SEXO - Menor 1 Año - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>COL06 - RANGO ETARIO Y SEXO - 1 año - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>COL06 - RANGO ETARIO Y SEXO - 1 año - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>COL06 - RANGO ETARIO Y SEXO - 1 año - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>COL07 - RANGO ETARIO Y SEXO - 1 año - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>COL07 - RANGO ETARIO Y SEXO - 1 año - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>COL07 - RANGO ETARIO Y SEXO - 1 año - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>COL08 - RANGO ETARIO Y SEXO - 2 a 4 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>COL08 - RANGO ETARIO Y SEXO - 2 a 4 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>COL08 - RANGO ETARIO Y SEXO - 2 a 4 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>COL09 - RANGO ETARIO Y SEXO - 2 a 4 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>COL09 - RANGO ETARIO Y SEXO - 2 a 4 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>COL09 - RANGO ETARIO Y SEXO - 2 a 4 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>COL10 - RANGO ETARIO Y SEXO - 5 a 9 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>COL10 - RANGO ETARIO Y SEXO - 5 a 9 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>COL10 - RANGO ETARIO Y SEXO - 5 a 9 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>COL11 - RANGO ETARIO Y SEXO - 5 a 9 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>COL11 - RANGO ETARIO Y SEXO - 5 a 9 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>COL11 - RANGO ETARIO Y SEXO - 5 a 9 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>COL12 - RANGO ETARIO Y SEXO - 10 a 14 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>COL12 - RANGO ETARIO Y SEXO - 10 a 14 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>COL12 - RANGO ETARIO Y SEXO - 10 a 14 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>COL13 - RANGO ETARIO Y SEXO - 10 a 14 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>COL13 - RANGO ETARIO Y SEXO - 10 a 14 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>COL13 - RANGO ETARIO Y SEXO - 10 a 14 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>COL14 - RANGO ETARIO Y SEXO - 15 a 19 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>COL14 - RANGO ETARIO Y SEXO - 15 a 19 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>COL14 - RANGO ETARIO Y SEXO - 15 a 19 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>COL15 - RANGO ETARIO Y SEXO - 15 a 19 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>COL15 - RANGO ETARIO Y SEXO - 15 a 19 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>COL15 - RANGO ETARIO Y SEXO - 15 a 19 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>COL16 - RANGO ETARIO Y SEXO - 20 a 24 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>COL16 - RANGO ETARIO Y SEXO - 20 a 24 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>COL16 - RANGO ETARIO Y SEXO - 20 a 24 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>COL17 - RANGO ETARIO Y SEXO - 20 a 24 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>COL17 - RANGO ETARIO Y SEXO - 20 a 24 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>COL17 - RANGO ETARIO Y SEXO - 20 a 24 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>COL18 - RANGO ETARIO Y SEXO - 25 a 29 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>COL18 - RANGO ETARIO Y SEXO - 25 a 29 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>COL18 - RANGO ETARIO Y SEXO - 25 a 29 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>COL19 - RANGO ETARIO Y SEXO - 25 a 29 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>COL19 - RANGO ETARIO Y SEXO - 25 a 29 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>COL19 - RANGO ETARIO Y SEXO - 25 a 29 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>COL20 - RANGO ETARIO Y SEXO - 30 a 34 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>COL20 - RANGO ETARIO Y SEXO - 30 a 34 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>COL20 - RANGO ETARIO Y SEXO - 30 a 34 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>COL21 - RANGO ETARIO Y SEXO - 30 a 34 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>COL21 - RANGO ETARIO Y SEXO - 30 a 34 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>COL21 - RANGO ETARIO Y SEXO - 30 a 34 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>COL22 - RANGO ETARIO Y SEXO - 35 a 39 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>COL22 - RANGO ETARIO Y SEXO - 35 a 39 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>COL22 - RANGO ETARIO Y SEXO - 35 a 39 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>COL23 - RANGO ETARIO Y SEXO - 35 a 39 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>COL23 - RANGO ETARIO Y SEXO - 35 a 39 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>COL23 - RANGO ETARIO Y SEXO - 35 a 39 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>COL24 - RANGO ETARIO Y SEXO - 40 a 44 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>COL24 - RANGO ETARIO Y SEXO - 40 a 44 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>COL24 - RANGO ETARIO Y SEXO - 40 a 44 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>COL25 - RANGO ETARIO Y SEXO - 40 a 44 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>COL25 - RANGO ETARIO Y SEXO - 40 a 44 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>COL25 - RANGO ETARIO Y SEXO - 40 a 44 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>COL26 - RANGO ETARIO Y SEXO - 45 a 49 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>COL26 - RANGO ETARIO Y SEXO - 45 a 49 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>COL26 - RANGO ETARIO Y SEXO - 45 a 49 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>COL27 - RANGO ETARIO Y SEXO - 45 a 49 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>COL27 - RANGO ETARIO Y SEXO - 45 a 49 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>COL27 - RANGO ETARIO Y SEXO - 45 a 49 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>COL28 - RANGO ETARIO Y SEXO - 50 a 54 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>COL28 - RANGO ETARIO Y SEXO - 50 a 54 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>COL28 - RANGO ETARIO Y SEXO - 50 a 54 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>COL29 - RANGO ETARIO Y SEXO - 50 a 54 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>COL29 - RANGO ETARIO Y SEXO - 50 a 54 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>COL29 - RANGO ETARIO Y SEXO - 50 a 54 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>COL30 - RANGO ETARIO Y SEXO - 55 a 59 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>COL30 - RANGO ETARIO Y SEXO - 55 a 59 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>COL30 - RANGO ETARIO Y SEXO - 55 a 59 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>COL31 - RANGO ETARIO Y SEXO - 55 a 59 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>COL31 - RANGO ETARIO Y SEXO - 55 a 59 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>COL31 - RANGO ETARIO Y SEXO - 55 a 59 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>COL32 - RANGO ETARIO Y SEXO - 60 a 64 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>COL32 - RANGO ETARIO Y SEXO - 60 a 64 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>COL32 - RANGO ETARIO Y SEXO - 60 a 64 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>COL33 - RANGO ETARIO Y SEXO - 60 a 64 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>COL33 - RANGO ETARIO Y SEXO - 60 a 64 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>COL33 - RANGO ETARIO Y SEXO - 60 a 64 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>COL34 - RANGO ETARIO Y SEXO - 65 a 69 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>COL34 - RANGO ETARIO Y SEXO - 65 a 69 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>COL34 - RANGO ETARIO Y SEXO - 65 a 69 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>COL35 - RANGO ETARIO Y SEXO - 65 a 69 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>COL35 - RANGO ETARIO Y SEXO - 65 a 69 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>COL35 - RANGO ETARIO Y SEXO - 65 a 69 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>COL36 - RANGO ETARIO Y SEXO - 70 a 74 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>COL36 - RANGO ETARIO Y SEXO - 70 a 74 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>COL36 - RANGO ETARIO Y SEXO - 70 a 74 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>COL37 - RANGO ETARIO Y SEXO - 70 a 74 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>COL37 - RANGO ETARIO Y SEXO - 70 a 74 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>COL37 - RANGO ETARIO Y SEXO - 70 a 74 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>COL38 - RANGO ETARIO Y SEXO - 75 a 79 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>COL38 - RANGO ETARIO Y SEXO - 75 a 79 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>COL38 - RANGO ETARIO Y SEXO - 75 a 79 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>COL39 - RANGO ETARIO Y SEXO - 75 a 79 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>COL39 - RANGO ETARIO Y SEXO - 75 a 79 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>COL39 - RANGO ETARIO Y SEXO - 75 a 79 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>COL40 - RANGO ETARIO Y SEXO - 80 y más años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>COL40 - RANGO ETARIO Y SEXO - 80 y más años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>COL40 - RANGO ETARIO Y SEXO - 80 y más años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>COL41 - RANGO ETARIO Y SEXO - 80 y más años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>COL41 - RANGO ETARIO Y SEXO - 80 y más años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>COL41 - RANGO ETARIO Y SEXO - 80 y más años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>COL42 - TRANS - Masculino | Mes 6</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>COL42 - TRANS - Masculino | Mes 12</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>COL42 - TRANS - Masculino | Diferencia</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>COL43 - TRANS - Femenino | Mes 6</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>COL43 - TRANS - Femenino | Mes 12</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>COL43 - TRANS - Femenino | Diferencia</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>COL44 - Pueblos Originarios | Mes 6</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>COL44 - Pueblos Originarios | Mes 12</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>COL44 - Pueblos Originarios | Diferencia</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>COL45 - Migrantes | Mes 6</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>COL45 - Migrantes | Mes 12</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>COL45 - Migrantes | Diferencia</t>
         </is>
       </c>
-      <c r="EU1" s="1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>COL46 - Niños, Niñas, Adolescentes y Jóvenes SENAME | Mes 6</t>
         </is>
       </c>
-      <c r="EV1" s="1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>COL46 - Niños, Niñas, Adolescentes y Jóvenes SENAME | Mes 12</t>
         </is>
       </c>
-      <c r="EW1" s="1" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>COL46 - Niños, Niñas, Adolescentes y Jóvenes SENAME | Diferencia</t>
         </is>
       </c>
-      <c r="EX1" s="1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>COL47 - Niños, Niñas, Adolescentes y Jóvenes Mejor Niñez | Mes 6</t>
         </is>
       </c>
-      <c r="EY1" s="1" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>COL47 - Niños, Niñas, Adolescentes y Jóvenes Mejor Niñez | Mes 12</t>
         </is>
       </c>
-      <c r="EZ1" s="1" t="inlineStr">
+      <c r="EZ1" t="inlineStr">
         <is>
           <t>COL47 - Niños, Niñas, Adolescentes y Jóvenes Mejor Niñez | Diferencia</t>
         </is>
@@ -8967,602 +8955,602 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Servicio de Salud</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Comuna</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Establecimiento</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo DEIS</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Prestacion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Detalle de prestacion</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Ano</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Codigo Servicio REM</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Codigo Comuna REM</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Total mes 6</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Total mes 12</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Diferencia</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Variacion %</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Alerta</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>COL01 - TOTAL - Ambos sexos | Mes 6</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>COL01 - TOTAL - Ambos sexos | Mes 12</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>COL01 - TOTAL - Ambos sexos | Diferencia</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>COL02 - TOTAL - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>COL02 - TOTAL - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>COL02 - TOTAL - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>COL03 - TOTAL - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>COL03 - TOTAL - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>COL03 - TOTAL - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>COL04 - RANGO ETARIO Y SEXO - 15 a 19 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>COL04 - RANGO ETARIO Y SEXO - 15 a 19 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>COL04 - RANGO ETARIO Y SEXO - 15 a 19 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>COL05 - RANGO ETARIO Y SEXO - 15 a 19 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>COL05 - RANGO ETARIO Y SEXO - 15 a 19 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>COL05 - RANGO ETARIO Y SEXO - 15 a 19 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>COL06 - RANGO ETARIO Y SEXO - 20 a 24 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>COL06 - RANGO ETARIO Y SEXO - 20 a 24 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>COL06 - RANGO ETARIO Y SEXO - 20 a 24 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>COL07 - RANGO ETARIO Y SEXO - 20 a 24 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>COL07 - RANGO ETARIO Y SEXO - 20 a 24 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>COL07 - RANGO ETARIO Y SEXO - 20 a 24 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>COL08 - RANGO ETARIO Y SEXO - 25 a 29 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>COL08 - RANGO ETARIO Y SEXO - 25 a 29 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>COL08 - RANGO ETARIO Y SEXO - 25 a 29 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>COL09 - RANGO ETARIO Y SEXO - 25 a 29 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>COL09 - RANGO ETARIO Y SEXO - 25 a 29 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>COL09 - RANGO ETARIO Y SEXO - 25 a 29 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>COL10 - RANGO ETARIO Y SEXO - 30 a 34 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>COL10 - RANGO ETARIO Y SEXO - 30 a 34 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>COL10 - RANGO ETARIO Y SEXO - 30 a 34 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>COL11 - RANGO ETARIO Y SEXO - 30 a 34 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>COL11 - RANGO ETARIO Y SEXO - 30 a 34 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>COL11 - RANGO ETARIO Y SEXO - 30 a 34 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>COL12 - RANGO ETARIO Y SEXO - 35 a 39 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>COL12 - RANGO ETARIO Y SEXO - 35 a 39 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>COL12 - RANGO ETARIO Y SEXO - 35 a 39 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>COL13 - RANGO ETARIO Y SEXO - 35 a 39 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>COL13 - RANGO ETARIO Y SEXO - 35 a 39 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>COL13 - RANGO ETARIO Y SEXO - 35 a 39 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>COL14 - RANGO ETARIO Y SEXO - 40 a 44 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>COL14 - RANGO ETARIO Y SEXO - 40 a 44 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>COL14 - RANGO ETARIO Y SEXO - 40 a 44 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>COL15 - RANGO ETARIO Y SEXO - 40 a 44 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>COL15 - RANGO ETARIO Y SEXO - 40 a 44 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>COL15 - RANGO ETARIO Y SEXO - 40 a 44 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>COL16 - RANGO ETARIO Y SEXO - 45 a 49 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>COL16 - RANGO ETARIO Y SEXO - 45 a 49 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>COL16 - RANGO ETARIO Y SEXO - 45 a 49 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>COL17 - RANGO ETARIO Y SEXO - 45 a 49 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>COL17 - RANGO ETARIO Y SEXO - 45 a 49 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>COL17 - RANGO ETARIO Y SEXO - 45 a 49 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>COL18 - RANGO ETARIO Y SEXO - 50 a 54 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>COL18 - RANGO ETARIO Y SEXO - 50 a 54 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>COL18 - RANGO ETARIO Y SEXO - 50 a 54 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>COL19 - RANGO ETARIO Y SEXO - 50 a 54 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>COL19 - RANGO ETARIO Y SEXO - 50 a 54 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>COL19 - RANGO ETARIO Y SEXO - 50 a 54 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>COL20 - RANGO ETARIO Y SEXO - 55 a 59 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>COL20 - RANGO ETARIO Y SEXO - 55 a 59 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>COL20 - RANGO ETARIO Y SEXO - 55 a 59 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>COL21 - RANGO ETARIO Y SEXO - 55 a 59 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>COL21 - RANGO ETARIO Y SEXO - 55 a 59 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>COL21 - RANGO ETARIO Y SEXO - 55 a 59 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>COL22 - RANGO ETARIO Y SEXO - 60 a 64 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>COL22 - RANGO ETARIO Y SEXO - 60 a 64 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>COL22 - RANGO ETARIO Y SEXO - 60 a 64 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>COL23 - RANGO ETARIO Y SEXO - 60 a 64 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>COL23 - RANGO ETARIO Y SEXO - 60 a 64 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>COL23 - RANGO ETARIO Y SEXO - 60 a 64 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>COL24 - RANGO ETARIO Y SEXO - 65 a 69 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>COL24 - RANGO ETARIO Y SEXO - 65 a 69 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>COL24 - RANGO ETARIO Y SEXO - 65 a 69 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>COL25 - RANGO ETARIO Y SEXO - 65 a 69 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>COL25 - RANGO ETARIO Y SEXO - 65 a 69 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>COL25 - RANGO ETARIO Y SEXO - 65 a 69 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>COL26 - RANGO ETARIO Y SEXO - 70 a 74 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>COL26 - RANGO ETARIO Y SEXO - 70 a 74 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>COL26 - RANGO ETARIO Y SEXO - 70 a 74 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>COL27 - RANGO ETARIO Y SEXO - 70 a 74 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>COL27 - RANGO ETARIO Y SEXO - 70 a 74 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>COL27 - RANGO ETARIO Y SEXO - 70 a 74 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>COL28 - RANGO ETARIO Y SEXO - 75 a 79 años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>COL28 - RANGO ETARIO Y SEXO - 75 a 79 años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>COL28 - RANGO ETARIO Y SEXO - 75 a 79 años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>COL29 - RANGO ETARIO Y SEXO - 75 a 79 años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>COL29 - RANGO ETARIO Y SEXO - 75 a 79 años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>COL29 - RANGO ETARIO Y SEXO - 75 a 79 años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>COL30 - RANGO ETARIO Y SEXO - 80 y más años - Hombres | Mes 6</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>COL30 - RANGO ETARIO Y SEXO - 80 y más años - Hombres | Mes 12</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>COL30 - RANGO ETARIO Y SEXO - 80 y más años - Hombres | Diferencia</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>COL31 - RANGO ETARIO Y SEXO - 80 y más años - Mujeres | Mes 6</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>COL31 - RANGO ETARIO Y SEXO - 80 y más años - Mujeres | Mes 12</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>COL31 - RANGO ETARIO Y SEXO - 80 y más años - Mujeres | Diferencia</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>COL32 - TRANS - Masculino | Mes 6</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>COL32 - TRANS - Masculino | Mes 12</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>COL32 - TRANS - Masculino | Diferencia</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>COL33 - TRANS - Femenino | Mes 6</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>COL33 - TRANS - Femenino | Mes 12</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>COL33 - TRANS - Femenino | Diferencia</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>COL34 - Pueblos Originarios | Mes 6</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>COL34 - Pueblos Originarios | Mes 12</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>COL34 - Pueblos Originarios | Diferencia</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>COL35 - Migrantes | Mes 6</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>COL35 - Migrantes | Mes 12</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>COL35 - Migrantes | Diferencia</t>
         </is>
